--- a/results/543_z13/2_canaliculi/543_z13_canaliculi_results.xlsx
+++ b/results/543_z13/2_canaliculi/543_z13_canaliculi_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,441 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>207.4787</v>
+      </c>
+      <c r="D12" t="n">
+        <v>205.0366</v>
+      </c>
+      <c r="E12" t="n">
+        <v>54.0901</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8447.8182</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8219</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1466.8964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>21999.7273</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21794</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3275.2139</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03624067</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03612809</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.00540695</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.04402843</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04358124</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00348523</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3.2312</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.5765</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>per 100 px</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>204.6364</v>
+      </c>
+      <c r="D20" t="n">
+        <v>192</v>
+      </c>
+      <c r="E20" t="n">
+        <v>75.6482</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>498.3636</v>
+      </c>
+      <c r="D21" t="n">
+        <v>412</v>
+      </c>
+      <c r="E21" t="n">
+        <v>253.3528</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>341.9271</v>
+      </c>
+      <c r="D22" t="n">
+        <v>347.6051</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60.217</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1087.2355</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1066.9626</v>
+      </c>
+      <c r="E23" t="n">
+        <v>125.6712</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8.0909</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.7002</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>11.7273</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.9014</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14.2727</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.149</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>11</v>
       </c>
     </row>
@@ -696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +1353,63 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_length_density_w_per_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.04958231</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_density_without_flagged_per_px</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.04380241</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_density_in_roi_per_px</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
         </is>
       </c>
     </row>
@@ -932,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1468,81 @@
           <t>mean_edge_length_px</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1001,6 +1568,51 @@
       </c>
       <c r="H2" t="n">
         <v>26.7644</v>
+      </c>
+      <c r="I2" t="n">
+        <v>205.0366</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="K2" t="n">
+        <v>22530</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03894576</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0448735</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.9017</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>278</v>
+      </c>
+      <c r="R2" t="n">
+        <v>651</v>
+      </c>
+      <c r="S2" t="n">
+        <v>391.7889</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1167.5849</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V2" t="n">
+        <v>13</v>
+      </c>
+      <c r="W2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1028,6 +1640,51 @@
       <c r="H3" t="n">
         <v>28.3691</v>
       </c>
+      <c r="I3" t="n">
+        <v>151.2965</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6982</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17707</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04439989</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04986728</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.6267</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>192</v>
+      </c>
+      <c r="R3" t="n">
+        <v>412</v>
+      </c>
+      <c r="S3" t="n">
+        <v>335.4508</v>
+      </c>
+      <c r="T3" t="n">
+        <v>979.1097</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1711,51 @@
       <c r="H4" t="n">
         <v>27.7276</v>
       </c>
+      <c r="I4" t="n">
+        <v>205.0366</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8219</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20045</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.04173257</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04370167</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.3895</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>218</v>
+      </c>
+      <c r="R4" t="n">
+        <v>388</v>
+      </c>
+      <c r="S4" t="n">
+        <v>388.8478</v>
+      </c>
+      <c r="T4" t="n">
+        <v>986.9626</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1782,51 @@
       <c r="H5" t="n">
         <v>36.8349</v>
       </c>
+      <c r="I5" t="n">
+        <v>139.6812</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6734</v>
+      </c>
+      <c r="K5" t="n">
+        <v>18999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03356103</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04358124</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.1477</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>120</v>
+      </c>
+      <c r="R5" t="n">
+        <v>286</v>
+      </c>
+      <c r="S5" t="n">
+        <v>259.0366</v>
+      </c>
+      <c r="T5" t="n">
+        <v>938.1219</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1106,6 +1853,51 @@
       <c r="H6" t="n">
         <v>27.928</v>
       </c>
+      <c r="I6" t="n">
+        <v>223.8234</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8900</v>
+      </c>
+      <c r="K6" t="n">
+        <v>23453</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.03662921</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04549525</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.2339</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>161</v>
+      </c>
+      <c r="R6" t="n">
+        <v>696</v>
+      </c>
+      <c r="S6" t="n">
+        <v>364.9066</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1191.4062</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1132,6 +1924,51 @@
       <c r="H7" t="n">
         <v>17.8085</v>
       </c>
+      <c r="I7" t="n">
+        <v>141.3381</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6516</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17817</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.04404543</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04832463</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.8301</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>189</v>
+      </c>
+      <c r="R7" t="n">
+        <v>271</v>
+      </c>
+      <c r="S7" t="n">
+        <v>327.0782</v>
+      </c>
+      <c r="T7" t="n">
+        <v>977.4356</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1158,6 +1995,51 @@
       <c r="H8" t="n">
         <v>20.9476</v>
       </c>
+      <c r="I8" t="n">
+        <v>254.9361</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9810</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24446</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03139653</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.04258365</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>139</v>
+      </c>
+      <c r="R8" t="n">
+        <v>252</v>
+      </c>
+      <c r="S8" t="n">
+        <v>347.6051</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1176.6438</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1184,6 +2066,51 @@
       <c r="H9" t="n">
         <v>26.9463</v>
       </c>
+      <c r="I9" t="n">
+        <v>278.5929</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10387</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26403</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.03051892</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03617013</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.5895</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>282</v>
+      </c>
+      <c r="R9" t="n">
+        <v>748</v>
+      </c>
+      <c r="S9" t="n">
+        <v>362.8772</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1095.1585</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1210,6 +2137,51 @@
       <c r="H10" t="n">
         <v>27.1599</v>
       </c>
+      <c r="I10" t="n">
+        <v>195.7229</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8083</v>
+      </c>
+      <c r="K10" t="n">
+        <v>21794</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03142398</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04331467</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.5765</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>220</v>
+      </c>
+      <c r="R10" t="n">
+        <v>664</v>
+      </c>
+      <c r="S10" t="n">
+        <v>282.8944</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1066.9626</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1236,6 +2208,51 @@
       <c r="H11" t="n">
         <v>30.1153</v>
       </c>
+      <c r="I11" t="n">
+        <v>184.9949</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7835</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21305</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02986599</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04308848</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.7028</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>102</v>
+      </c>
+      <c r="R11" t="n">
+        <v>166</v>
+      </c>
+      <c r="S11" t="n">
+        <v>250.8234</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1024.3351</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1261,6 +2278,51 @@
       </c>
       <c r="H12" t="n">
         <v>25.2166</v>
+      </c>
+      <c r="I12" t="n">
+        <v>301.8061</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10961</v>
+      </c>
+      <c r="K12" t="n">
+        <v>27498</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.03612809</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04331224</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.9761</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>350</v>
+      </c>
+      <c r="R12" t="n">
+        <v>948</v>
+      </c>
+      <c r="S12" t="n">
+        <v>449.8894</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1355.8692</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12</v>
+      </c>
+      <c r="V12" t="n">
+        <v>14</v>
+      </c>
+      <c r="W12" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
